--- a/ChurnedCompaniesWithCallsAndTicketsUpdated.xlsx
+++ b/ChurnedCompaniesWithCallsAndTicketsUpdated.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="308">
   <si>
     <t>Company_Name</t>
   </si>
@@ -803,6 +803,21 @@
   </si>
   <si>
     <t>SOL OG STRAND FERIEHUSUDLEJNING A/S</t>
+  </si>
+  <si>
+    <t>SL FONDEN</t>
+  </si>
+  <si>
+    <t>TT-NETVÆRKET P/S</t>
+  </si>
+  <si>
+    <t>MIKKELSEN ELECTRONICS A/S</t>
+  </si>
+  <si>
+    <t>KABOOKI A/S</t>
+  </si>
+  <si>
+    <t>DANSK HESTEVÆDDELØB APS</t>
   </si>
   <si>
     <t>30</t>
@@ -1280,7 +1295,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C388"/>
+  <dimension ref="A1:C396"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1726,7 +1741,7 @@
         <v>28</v>
       </c>
       <c r="B46" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -1824,7 +1839,7 @@
         <v>34</v>
       </c>
       <c r="B56" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -1868,7 +1883,7 @@
         <v>38</v>
       </c>
       <c r="B60" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C60">
         <v>16</v>
@@ -2090,7 +2105,7 @@
         <v>54</v>
       </c>
       <c r="B81" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -2112,7 +2127,7 @@
         <v>56</v>
       </c>
       <c r="B83" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C83">
         <v>0</v>
@@ -2123,7 +2138,7 @@
         <v>56</v>
       </c>
       <c r="B84" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -2232,7 +2247,7 @@
         <v>61</v>
       </c>
       <c r="B95" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -2265,7 +2280,7 @@
         <v>64</v>
       </c>
       <c r="B98" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -2287,7 +2302,7 @@
         <v>66</v>
       </c>
       <c r="B100" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -2541,7 +2556,7 @@
         <v>81</v>
       </c>
       <c r="B125" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C125">
         <v>0</v>
@@ -2585,7 +2600,7 @@
         <v>85</v>
       </c>
       <c r="B129" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C129">
         <v>0</v>
@@ -2670,7 +2685,7 @@
         <v>91</v>
       </c>
       <c r="B137" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C137">
         <v>8</v>
@@ -2681,7 +2696,7 @@
         <v>91</v>
       </c>
       <c r="B138" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C138">
         <v>8</v>
@@ -2692,7 +2707,7 @@
         <v>92</v>
       </c>
       <c r="B139" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C139">
         <v>0</v>
@@ -2733,7 +2748,7 @@
         <v>95</v>
       </c>
       <c r="B143" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="C143">
         <v>277</v>
@@ -2766,7 +2781,7 @@
         <v>98</v>
       </c>
       <c r="B146" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -2804,7 +2819,7 @@
         <v>100</v>
       </c>
       <c r="B150" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -2845,7 +2860,7 @@
         <v>103</v>
       </c>
       <c r="B154" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C154">
         <v>1161</v>
@@ -2919,7 +2934,7 @@
         <v>109</v>
       </c>
       <c r="B161" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -2938,7 +2953,7 @@
         <v>110</v>
       </c>
       <c r="B163" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -2982,7 +2997,7 @@
         <v>113</v>
       </c>
       <c r="B167" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C167">
         <v>0</v>
@@ -2993,7 +3008,7 @@
         <v>114</v>
       </c>
       <c r="B168" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -3004,7 +3019,7 @@
         <v>115</v>
       </c>
       <c r="B169" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C169">
         <v>0</v>
@@ -3056,7 +3071,7 @@
         <v>118</v>
       </c>
       <c r="B174" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C174">
         <v>0</v>
@@ -3067,7 +3082,7 @@
         <v>119</v>
       </c>
       <c r="B175" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C175">
         <v>0</v>
@@ -3130,7 +3145,7 @@
         <v>124</v>
       </c>
       <c r="B181" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -3160,7 +3175,7 @@
         <v>126</v>
       </c>
       <c r="B184" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -3190,7 +3205,7 @@
         <v>128</v>
       </c>
       <c r="B187" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="C187">
         <v>0</v>
@@ -3201,7 +3216,7 @@
         <v>129</v>
       </c>
       <c r="B188" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C188">
         <v>52</v>
@@ -3212,7 +3227,7 @@
         <v>130</v>
       </c>
       <c r="B189" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C189">
         <v>0</v>
@@ -3223,7 +3238,7 @@
         <v>131</v>
       </c>
       <c r="B190" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="C190">
         <v>0</v>
@@ -3256,7 +3271,7 @@
         <v>134</v>
       </c>
       <c r="B193" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C193">
         <v>123</v>
@@ -3305,7 +3320,7 @@
         <v>137</v>
       </c>
       <c r="B198" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="C198">
         <v>213</v>
@@ -3324,7 +3339,7 @@
         <v>138</v>
       </c>
       <c r="B200" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C200">
         <v>0</v>
@@ -3335,7 +3350,7 @@
         <v>139</v>
       </c>
       <c r="B201" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="C201">
         <v>0</v>
@@ -3346,7 +3361,7 @@
         <v>139</v>
       </c>
       <c r="B202" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="C202">
         <v>0</v>
@@ -3357,7 +3372,7 @@
         <v>139</v>
       </c>
       <c r="B203" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="C203">
         <v>0</v>
@@ -3368,7 +3383,7 @@
         <v>140</v>
       </c>
       <c r="B204" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C204">
         <v>0</v>
@@ -3401,7 +3416,7 @@
         <v>143</v>
       </c>
       <c r="B207" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="C207">
         <v>0</v>
@@ -3431,7 +3446,7 @@
         <v>145</v>
       </c>
       <c r="B210" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C210">
         <v>155</v>
@@ -3494,7 +3509,7 @@
         <v>149</v>
       </c>
       <c r="B216" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="C216">
         <v>0</v>
@@ -3543,7 +3558,7 @@
         <v>152</v>
       </c>
       <c r="B221" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C221">
         <v>0</v>
@@ -3565,7 +3580,7 @@
         <v>154</v>
       </c>
       <c r="B223" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="C223">
         <v>0</v>
@@ -3576,7 +3591,7 @@
         <v>155</v>
       </c>
       <c r="B224" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C224">
         <v>42</v>
@@ -3587,7 +3602,7 @@
         <v>156</v>
       </c>
       <c r="B225" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C225">
         <v>0</v>
@@ -3598,7 +3613,7 @@
         <v>156</v>
       </c>
       <c r="B226" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C226">
         <v>0</v>
@@ -3609,7 +3624,7 @@
         <v>157</v>
       </c>
       <c r="B227" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="C227">
         <v>0</v>
@@ -3628,7 +3643,7 @@
         <v>158</v>
       </c>
       <c r="B229" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="C229">
         <v>0</v>
@@ -3639,7 +3654,7 @@
         <v>159</v>
       </c>
       <c r="B230" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="C230">
         <v>0</v>
@@ -3661,7 +3676,7 @@
         <v>161</v>
       </c>
       <c r="B232" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="C232">
         <v>0</v>
@@ -3672,7 +3687,7 @@
         <v>162</v>
       </c>
       <c r="B233" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="C233">
         <v>0</v>
@@ -3702,7 +3717,7 @@
         <v>164</v>
       </c>
       <c r="B236" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C236">
         <v>0</v>
@@ -3724,7 +3739,7 @@
         <v>165</v>
       </c>
       <c r="B238" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C238">
         <v>66</v>
@@ -3735,7 +3750,7 @@
         <v>166</v>
       </c>
       <c r="B239" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C239">
         <v>0</v>
@@ -3765,7 +3780,7 @@
         <v>168</v>
       </c>
       <c r="B242" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C242">
         <v>0</v>
@@ -3776,7 +3791,7 @@
         <v>169</v>
       </c>
       <c r="B243" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C243">
         <v>0</v>
@@ -3787,7 +3802,7 @@
         <v>170</v>
       </c>
       <c r="B244" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C244">
         <v>2</v>
@@ -3798,7 +3813,7 @@
         <v>170</v>
       </c>
       <c r="B245" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="C245">
         <v>2</v>
@@ -3809,7 +3824,7 @@
         <v>171</v>
       </c>
       <c r="B246" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="C246">
         <v>2</v>
@@ -3820,7 +3835,7 @@
         <v>171</v>
       </c>
       <c r="B247" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="C247">
         <v>2</v>
@@ -3831,7 +3846,7 @@
         <v>171</v>
       </c>
       <c r="B248" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="C248">
         <v>2</v>
@@ -3842,7 +3857,7 @@
         <v>38</v>
       </c>
       <c r="B249" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="C249">
         <v>16</v>
@@ -3853,7 +3868,7 @@
         <v>172</v>
       </c>
       <c r="B250" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C250">
         <v>0</v>
@@ -3864,7 +3879,7 @@
         <v>173</v>
       </c>
       <c r="B251" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="C251">
         <v>0</v>
@@ -3875,7 +3890,7 @@
         <v>174</v>
       </c>
       <c r="B252" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="C252">
         <v>0</v>
@@ -3886,7 +3901,7 @@
         <v>175</v>
       </c>
       <c r="B253" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C253">
         <v>0</v>
@@ -3965,7 +3980,7 @@
         <v>180</v>
       </c>
       <c r="B261" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="C261">
         <v>0</v>
@@ -3976,7 +3991,7 @@
         <v>181</v>
       </c>
       <c r="B262" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C262">
         <v>0</v>
@@ -3987,7 +4002,7 @@
         <v>181</v>
       </c>
       <c r="B263" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C263">
         <v>0</v>
@@ -3998,7 +4013,7 @@
         <v>182</v>
       </c>
       <c r="B264" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="C264">
         <v>0</v>
@@ -4009,7 +4024,7 @@
         <v>183</v>
       </c>
       <c r="B265" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C265">
         <v>0</v>
@@ -4050,7 +4065,7 @@
         <v>186</v>
       </c>
       <c r="B269" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="C269">
         <v>190</v>
@@ -4069,7 +4084,7 @@
         <v>187</v>
       </c>
       <c r="B271" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C271">
         <v>0</v>
@@ -4080,7 +4095,7 @@
         <v>187</v>
       </c>
       <c r="B272" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="C272">
         <v>0</v>
@@ -4091,7 +4106,7 @@
         <v>188</v>
       </c>
       <c r="B273" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C273">
         <v>0</v>
@@ -4102,7 +4117,7 @@
         <v>189</v>
       </c>
       <c r="B274" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C274">
         <v>70</v>
@@ -4113,7 +4128,7 @@
         <v>189</v>
       </c>
       <c r="B275" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C275">
         <v>70</v>
@@ -4135,7 +4150,7 @@
         <v>191</v>
       </c>
       <c r="B277" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="C277">
         <v>0</v>
@@ -4146,7 +4161,7 @@
         <v>192</v>
       </c>
       <c r="B278" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="C278">
         <v>0</v>
@@ -4168,7 +4183,7 @@
         <v>194</v>
       </c>
       <c r="B280" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C280">
         <v>0</v>
@@ -4187,7 +4202,7 @@
         <v>195</v>
       </c>
       <c r="B282" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C282">
         <v>0</v>
@@ -4198,7 +4213,7 @@
         <v>196</v>
       </c>
       <c r="B283" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="C283">
         <v>0</v>
@@ -4231,7 +4246,7 @@
         <v>199</v>
       </c>
       <c r="B286" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C286">
         <v>0</v>
@@ -4250,7 +4265,7 @@
         <v>200</v>
       </c>
       <c r="B288" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="C288">
         <v>0</v>
@@ -4261,7 +4276,7 @@
         <v>200</v>
       </c>
       <c r="B289" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="C289">
         <v>0</v>
@@ -4283,7 +4298,7 @@
         <v>202</v>
       </c>
       <c r="B291" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C291">
         <v>0</v>
@@ -4340,7 +4355,7 @@
         <v>205</v>
       </c>
       <c r="B297" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C297">
         <v>0</v>
@@ -4359,7 +4374,7 @@
         <v>206</v>
       </c>
       <c r="B299" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C299">
         <v>0</v>
@@ -4370,7 +4385,7 @@
         <v>207</v>
       </c>
       <c r="B300" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="C300">
         <v>0</v>
@@ -4389,7 +4404,7 @@
         <v>208</v>
       </c>
       <c r="B302" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C302">
         <v>0</v>
@@ -4400,7 +4415,7 @@
         <v>209</v>
       </c>
       <c r="B303" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C303">
         <v>0</v>
@@ -4411,7 +4426,7 @@
         <v>209</v>
       </c>
       <c r="B304" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C304">
         <v>0</v>
@@ -4422,7 +4437,7 @@
         <v>210</v>
       </c>
       <c r="B305" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="C305">
         <v>0</v>
@@ -4460,7 +4475,7 @@
         <v>212</v>
       </c>
       <c r="B309" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C309">
         <v>0</v>
@@ -4471,7 +4486,7 @@
         <v>213</v>
       </c>
       <c r="B310" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C310">
         <v>0</v>
@@ -4493,7 +4508,7 @@
         <v>215</v>
       </c>
       <c r="B312" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C312">
         <v>226</v>
@@ -4504,7 +4519,7 @@
         <v>216</v>
       </c>
       <c r="B313" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C313">
         <v>45</v>
@@ -4526,7 +4541,7 @@
         <v>218</v>
       </c>
       <c r="B315" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C315">
         <v>76</v>
@@ -4537,7 +4552,7 @@
         <v>219</v>
       </c>
       <c r="B316" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C316">
         <v>109</v>
@@ -4559,7 +4574,7 @@
         <v>221</v>
       </c>
       <c r="B318" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C318">
         <v>127</v>
@@ -4570,7 +4585,7 @@
         <v>222</v>
       </c>
       <c r="B319" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C319">
         <v>0</v>
@@ -4581,7 +4596,7 @@
         <v>222</v>
       </c>
       <c r="B320" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C320">
         <v>0</v>
@@ -4600,7 +4615,7 @@
         <v>223</v>
       </c>
       <c r="B322" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C322">
         <v>296</v>
@@ -4611,7 +4626,7 @@
         <v>223</v>
       </c>
       <c r="B323" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C323">
         <v>296</v>
@@ -4633,7 +4648,7 @@
         <v>225</v>
       </c>
       <c r="B325" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C325">
         <v>121</v>
@@ -4644,7 +4659,7 @@
         <v>226</v>
       </c>
       <c r="B326" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C326">
         <v>0</v>
@@ -4655,7 +4670,7 @@
         <v>227</v>
       </c>
       <c r="B327" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="C327">
         <v>0</v>
@@ -4688,7 +4703,7 @@
         <v>230</v>
       </c>
       <c r="B330" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C330">
         <v>0</v>
@@ -4707,7 +4722,7 @@
         <v>231</v>
       </c>
       <c r="B332" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="C332">
         <v>0</v>
@@ -4718,7 +4733,7 @@
         <v>232</v>
       </c>
       <c r="B333" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C333">
         <v>0</v>
@@ -4729,7 +4744,7 @@
         <v>233</v>
       </c>
       <c r="B334" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="C334">
         <v>0</v>
@@ -4748,7 +4763,7 @@
         <v>234</v>
       </c>
       <c r="B336" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="C336">
         <v>0</v>
@@ -4759,7 +4774,7 @@
         <v>234</v>
       </c>
       <c r="B337" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="C337">
         <v>0</v>
@@ -4816,7 +4831,7 @@
         <v>237</v>
       </c>
       <c r="B343" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C343">
         <v>0</v>
@@ -4827,7 +4842,7 @@
         <v>237</v>
       </c>
       <c r="B344" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C344">
         <v>0</v>
@@ -4838,7 +4853,7 @@
         <v>237</v>
       </c>
       <c r="B345" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C345">
         <v>0</v>
@@ -4849,7 +4864,7 @@
         <v>238</v>
       </c>
       <c r="B346" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C346">
         <v>0</v>
@@ -4860,7 +4875,7 @@
         <v>239</v>
       </c>
       <c r="B347" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="C347">
         <v>0</v>
@@ -4871,7 +4886,7 @@
         <v>210</v>
       </c>
       <c r="B348" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="C348">
         <v>0</v>
@@ -4882,7 +4897,7 @@
         <v>240</v>
       </c>
       <c r="B349" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C349">
         <v>0</v>
@@ -4909,7 +4924,7 @@
         <v>241</v>
       </c>
       <c r="B352" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="C352">
         <v>0</v>
@@ -4920,7 +4935,7 @@
         <v>241</v>
       </c>
       <c r="B353" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="C353">
         <v>0</v>
@@ -4931,7 +4946,7 @@
         <v>237</v>
       </c>
       <c r="B354" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C354">
         <v>0</v>
@@ -4942,7 +4957,7 @@
         <v>237</v>
       </c>
       <c r="B355" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C355">
         <v>0</v>
@@ -4953,7 +4968,7 @@
         <v>237</v>
       </c>
       <c r="B356" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="C356">
         <v>0</v>
@@ -4986,7 +5001,7 @@
         <v>243</v>
       </c>
       <c r="B359" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C359">
         <v>0</v>
@@ -4997,7 +5012,7 @@
         <v>244</v>
       </c>
       <c r="B360" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="C360">
         <v>0</v>
@@ -5046,7 +5061,7 @@
         <v>247</v>
       </c>
       <c r="B365" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C365">
         <v>85</v>
@@ -5057,7 +5072,7 @@
         <v>248</v>
       </c>
       <c r="B366" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="C366">
         <v>0</v>
@@ -5068,7 +5083,7 @@
         <v>249</v>
       </c>
       <c r="B367" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C367">
         <v>0</v>
@@ -5079,7 +5094,7 @@
         <v>249</v>
       </c>
       <c r="B368" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C368">
         <v>0</v>
@@ -5090,7 +5105,7 @@
         <v>249</v>
       </c>
       <c r="B369" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C369">
         <v>0</v>
@@ -5101,7 +5116,7 @@
         <v>249</v>
       </c>
       <c r="B370" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C370">
         <v>0</v>
@@ -5112,7 +5127,7 @@
         <v>250</v>
       </c>
       <c r="B371" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C371">
         <v>126</v>
@@ -5123,7 +5138,7 @@
         <v>251</v>
       </c>
       <c r="B372" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C372">
         <v>0</v>
@@ -5134,7 +5149,7 @@
         <v>252</v>
       </c>
       <c r="B373" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="C373">
         <v>0</v>
@@ -5145,7 +5160,7 @@
         <v>253</v>
       </c>
       <c r="B374" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="C374">
         <v>0</v>
@@ -5156,7 +5171,7 @@
         <v>254</v>
       </c>
       <c r="B375" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="C375">
         <v>0</v>
@@ -5194,7 +5209,7 @@
         <v>256</v>
       </c>
       <c r="B379" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C379">
         <v>57</v>
@@ -5205,7 +5220,7 @@
         <v>256</v>
       </c>
       <c r="B380" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C380">
         <v>57</v>
@@ -5216,7 +5231,7 @@
         <v>257</v>
       </c>
       <c r="B381" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C381">
         <v>146</v>
@@ -5227,7 +5242,7 @@
         <v>218</v>
       </c>
       <c r="B382" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C382">
         <v>76</v>
@@ -5238,7 +5253,7 @@
         <v>258</v>
       </c>
       <c r="B383" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C383">
         <v>0</v>
@@ -5249,7 +5264,7 @@
         <v>259</v>
       </c>
       <c r="B384" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C384">
         <v>18</v>
@@ -5260,7 +5275,7 @@
         <v>259</v>
       </c>
       <c r="B385" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C385">
         <v>18</v>
@@ -5271,7 +5286,7 @@
         <v>260</v>
       </c>
       <c r="B386" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C386">
         <v>0</v>
@@ -5282,7 +5297,7 @@
         <v>261</v>
       </c>
       <c r="B387" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="C387">
         <v>0</v>
@@ -5293,9 +5308,94 @@
         <v>262</v>
       </c>
       <c r="B388" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="C388">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3">
+      <c r="A389" t="s">
+        <v>263</v>
+      </c>
+      <c r="B389" t="s">
+        <v>295</v>
+      </c>
+      <c r="C389">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3">
+      <c r="A390" t="s">
+        <v>264</v>
+      </c>
+      <c r="B390" t="s">
+        <v>269</v>
+      </c>
+      <c r="C390">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3">
+      <c r="B391">
+        <v>0</v>
+      </c>
+      <c r="C391">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3">
+      <c r="A392" t="s">
+        <v>265</v>
+      </c>
+      <c r="B392" t="s">
+        <v>270</v>
+      </c>
+      <c r="C392">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3">
+      <c r="A393" t="s">
+        <v>265</v>
+      </c>
+      <c r="B393" t="s">
+        <v>270</v>
+      </c>
+      <c r="C393">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3">
+      <c r="A394" t="s">
+        <v>266</v>
+      </c>
+      <c r="B394" t="s">
+        <v>282</v>
+      </c>
+      <c r="C394">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3">
+      <c r="A395" t="s">
+        <v>266</v>
+      </c>
+      <c r="B395" t="s">
+        <v>282</v>
+      </c>
+      <c r="C395">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="396" spans="1:3">
+      <c r="A396" t="s">
+        <v>267</v>
+      </c>
+      <c r="B396">
+        <v>0</v>
+      </c>
+      <c r="C396">
         <v>0</v>
       </c>
     </row>
